--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>115273679</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57535</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115273679</v>
       </c>
       <c r="B2" t="n">
-        <v>57535</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115273679</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57544</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125113655</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56772</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Hult, Hult, Nyeds f.g, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>433918</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>125113655</v>
       </c>
       <c r="B5" t="n">
-        <v>56772</v>
+        <v>57460</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1055,12 +1055,7 @@
         <v>125113655</v>
       </c>
       <c r="B5" t="n">
-        <v>57460</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,6 +1169,244 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130889854</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östra Hult, Hult, Nyeds f.g, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>433918</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130889857</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Östra Hult, Hult, Nyeds f.g, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>433918</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130889857</v>
+        <v>130889854</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,26 +1182,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130889854</v>
+        <v>130889857</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>57881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1171,10 +1171,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130889854</v>
+        <v>130889857</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,26 +1182,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130889857</v>
+        <v>130889854</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>58043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,26 +1301,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,6 +1526,244 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133588452</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Östra Hult, Hult, Nyeds f.g, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>433918</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133588428</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58291</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östra Hult, Hult, Nyeds f.g, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>433918</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6605588</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karin Bergh</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1531,7 +1531,7 @@
         <v>133588452</v>
       </c>
       <c r="B9" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>133588428</v>
       </c>
       <c r="B10" t="n">
-        <v>58291</v>
+        <v>58298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -1531,7 +1531,7 @@
         <v>133588452</v>
       </c>
       <c r="B9" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>133588428</v>
       </c>
       <c r="B10" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115273679</v>
+        <v>130889857</v>
       </c>
       <c r="B2" t="n">
-        <v>57544</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102623</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +797,7 @@
         <v>115357402</v>
       </c>
       <c r="B3" t="n">
-        <v>56611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,16 +916,11 @@
         <v>120666061</v>
       </c>
       <c r="B4" t="n">
-        <v>57298</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1052,27 +1037,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113655</v>
+        <v>115273679</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>58129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102976</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,14 +1067,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1129,22 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1171,27 +1156,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130889857</v>
+        <v>125113655</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>102976</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1201,14 +1186,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1248,22 +1233,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,44 +1275,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130889854</v>
+        <v>133588428</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>58308</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1367,22 +1352,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,44 +1394,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132402723</v>
+        <v>133588452</v>
       </c>
       <c r="B8" t="n">
-        <v>58680</v>
+        <v>58461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1486,22 +1471,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133588452</v>
+        <v>130889854</v>
       </c>
       <c r="B9" t="n">
-        <v>58461</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,33 +1524,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1605,22 +1590,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133588428</v>
+        <v>132402723</v>
       </c>
       <c r="B10" t="n">
-        <v>58308</v>
+        <v>58698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,33 +1643,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103008</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1724,22 +1709,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 69506-2021 artfynd.xlsx
+++ b/artfynd/A 69506-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130889857</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115357402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120666061</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115273679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125113655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1391,6 +1421,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133588428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1510,6 +1545,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133588452</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1629,6 +1669,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130889854</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1748,8 +1793,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132402723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>